--- a/Master/7182r00/7182r00 @ 0.250 IPR_cutlet_data.xlsx
+++ b/Master/7182r00/7182r00 @ 0.250 IPR_cutlet_data.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -894,202 +894,262 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>3.119</v>
+        <v>1.226</v>
       </c>
       <c r="B23" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>3.4726</v>
+        <v>3.3679</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>-0.202</v>
+        <v>-1.385</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.0259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>2.12</v>
+        <v>1.231</v>
       </c>
       <c r="B24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C24" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="D24" s="7" t="n">
-        <v>3.5737</v>
+        <v>3.4197</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>-0.3846</v>
+        <v>-2.1072</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0236</v>
+        <v>0.0007</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>1.121</v>
+        <v>2.23</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>3.659</v>
+        <v>3.4202</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>-0.5727</v>
+        <v>-1.9129</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>0.0198</v>
+        <v>0.0008</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>5.122</v>
+        <v>3.119</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>3.734</v>
+        <v>3.4726</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>-0.5185999999999999</v>
+        <v>-0.202</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>0.0173</v>
+        <v>0.0259</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>4.123</v>
+        <v>2.12</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>3.7964</v>
+        <v>3.5737</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>-0.7258</v>
+        <v>-0.3846</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>0.0142</v>
+        <v>0.0236</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>3.124</v>
+        <v>1.121</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>3.8454</v>
+        <v>3.659</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>-0.9422</v>
+        <v>-0.5727</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0198</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>2.125</v>
+        <v>5.122</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>3.8774</v>
+        <v>3.734</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>-1.1539</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>0.0061</v>
+        <v>0.0173</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>1.126</v>
+        <v>4.123</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>3.8946</v>
+        <v>3.7964</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>-1.3517</v>
+        <v>-0.7258</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>0.0023</v>
+        <v>0.0142</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
+        <v>3.124</v>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>3.8454</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>-0.9422</v>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>0.009599999999999999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>3.8774</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>-1.1539</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>0.0061</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
+        <v>1.126</v>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>3.8946</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>-1.3517</v>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>0.0023</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
         <v>5.127</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B34" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C31" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="7" t="n">
+      <c r="C34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="7" t="n">
         <v>3.9011</v>
       </c>
-      <c r="E31" s="7" t="n">
+      <c r="E34" s="7" t="n">
         <v>-1.3009</v>
       </c>
-      <c r="F31" s="7" t="n">
+      <c r="F34" s="7" t="n">
         <v>0.0008</v>
       </c>
     </row>
-    <row r="33">
-      <c r="E33" s="8" t="inlineStr">
+    <row r="36">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>Count:</t>
         </is>
       </c>
-      <c r="F33" s="9" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="E34" s="8" t="inlineStr">
+      <c r="F36" s="9" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>Total Area:</t>
         </is>
       </c>
-      <c r="F34" s="10" t="n">
-        <v>0.965</v>
+      <c r="F37" s="10" t="n">
+        <v>0.9665</v>
       </c>
     </row>
   </sheetData>
